--- a/Assets/Data/DataTable/03_Buf_Table.xlsx
+++ b/Assets/Data/DataTable/03_Buf_Table.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE2B245-0FC7-42DB-9767-16CDFE4E57B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA02BCD1-DF06-49D3-B4DE-9716D3CD3775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
     <sheet name="!Desc" sheetId="1" r:id="rId2"/>
-    <sheet name="!Sample" sheetId="3" r:id="rId3"/>
+    <sheet name="BufTable" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Assets/Data/DataTable/03_Buf_Table.xlsx
+++ b/Assets/Data/DataTable/03_Buf_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA02BCD1-DF06-49D3-B4DE-9716D3CD3775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4174B785-3716-44A7-AC4F-5F0653E8D75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -413,13 +413,23 @@
 5: 치명타 확률
 6: 치명타 데미지 배율
 7: 카운터 데미지 배율
-8: 속성 게이지 효율 계수
-9: 속성 게이지 저항 계수
-10: 속성 과부하 계수
-11: 받는 피해 증가
-12: 받는 피해 감소
-13: SP 소모량 증가
-14: 도발</t>
+8: 물리 속성 게이지 효율 계수
+9: 화염 속성 게이지 효율 계수
+10: 방사능 속성 게이지 효율 계수
+11: 중력 속성 게이지 효율 계수
+12: 공허 속성 게이지 효율 계수
+13: 신성 속성 게이지 효율 계수
+14: 속성 게이지 저항 계수
+15: 물리 속성 과부하 계수
+16: 화염 속성 과부하 계수
+17: 방사능 속성 과부하 계수
+18: 중력 속성 과부하 계수
+19: 공허 속성 과부하 계수
+20: 신성 속성 과부하 계수
+21: 받는 피해 증가
+22: 받는 피해 감소
+23: SP 소모량 증가
+24: 도발</t>
         </r>
       </text>
     </comment>
@@ -455,7 +465,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="93">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -797,6 +807,17 @@
   </si>
   <si>
     <t>Calculate_Mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보정 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>Buf_Value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -804,8 +825,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="00"/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -948,7 +971,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1045,6 +1068,18 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1062,6 +1097,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFA7A7"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3701,19 +3741,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" style="30" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" style="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.625" style="31" customWidth="1"/>
     <col min="6" max="6" width="19.375" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.125" customWidth="1"/>
+    <col min="7" max="7" width="22.125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -3722,8 +3762,9 @@
       <c r="D1"/>
       <c r="E1"/>
       <c r="F1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>77</v>
       </c>
@@ -3742,8 +3783,11 @@
       <c r="F2" s="22" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+      <c r="G2" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>70</v>
       </c>
@@ -3762,8 +3806,12 @@
       <c r="F3" s="29" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+      <c r="G3" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="M3"/>
+    </row>
+    <row r="4" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>55</v>
       </c>
@@ -3782,8 +3830,12 @@
       <c r="F4" s="26" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="M4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>30001001</v>
@@ -3791,7 +3843,7 @@
       <c r="B5" s="25">
         <v>30</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="32">
         <v>0</v>
       </c>
       <c r="D5" s="25">
@@ -3803,8 +3855,11 @@
       <c r="F5" s="24">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <f>(B6*1000000) + (C6*10000) + D6</f>
         <v>30011002</v>
@@ -3812,276 +3867,1026 @@
       <c r="B6" s="25">
         <v>30</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="32">
         <v>1</v>
       </c>
       <c r="D6" s="25">
         <v>1002</v>
       </c>
       <c r="E6" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="24">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
-        <f t="shared" ref="A7:A18" si="0">(B7*1000000) + (C7*10000) + D7</f>
-        <v>30021003</v>
+        <f t="shared" ref="A7:A20" si="0">(B7*1000000) + (C7*10000) + D7</f>
+        <v>30001003</v>
       </c>
       <c r="B7" s="25">
         <v>30</v>
       </c>
-      <c r="C7" s="25">
-        <v>2</v>
+      <c r="C7" s="32">
+        <v>0</v>
       </c>
       <c r="D7" s="25">
         <v>1003</v>
       </c>
       <c r="E7" s="24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="24">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <f t="shared" si="0"/>
-        <v>30031004</v>
+        <v>30011004</v>
       </c>
       <c r="B8" s="25">
         <v>30</v>
       </c>
-      <c r="C8" s="25">
-        <v>3</v>
+      <c r="C8" s="32">
+        <v>1</v>
       </c>
       <c r="D8" s="25">
         <v>1004</v>
       </c>
       <c r="E8" s="24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <f t="shared" si="0"/>
-        <v>30041005</v>
+        <v>30001005</v>
       </c>
       <c r="B9" s="25">
         <v>30</v>
       </c>
-      <c r="C9" s="25">
-        <v>4</v>
+      <c r="C9" s="32">
+        <v>0</v>
       </c>
       <c r="D9" s="25">
         <v>1005</v>
       </c>
       <c r="E9" s="24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <f t="shared" si="0"/>
-        <v>30051006</v>
+        <v>30001006</v>
       </c>
       <c r="B10" s="25">
         <v>30</v>
       </c>
-      <c r="C10" s="25">
-        <v>5</v>
+      <c r="C10" s="32">
+        <v>0</v>
       </c>
       <c r="D10" s="25">
         <v>1006</v>
       </c>
       <c r="E10" s="24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <f t="shared" si="0"/>
-        <v>30061007</v>
+        <v>30011007</v>
       </c>
       <c r="B11" s="25">
         <v>30</v>
       </c>
-      <c r="C11" s="25">
-        <v>6</v>
+      <c r="C11" s="32">
+        <v>1</v>
       </c>
       <c r="D11" s="25">
         <v>1007</v>
       </c>
       <c r="E11" s="24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F11" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="G11" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <f t="shared" si="0"/>
-        <v>30071008</v>
+        <v>30001008</v>
       </c>
       <c r="B12" s="25">
         <v>30</v>
       </c>
-      <c r="C12" s="25">
-        <v>7</v>
+      <c r="C12" s="32">
+        <v>0</v>
       </c>
       <c r="D12" s="25">
         <v>1008</v>
       </c>
       <c r="E12" s="24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" s="24">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <f t="shared" si="0"/>
-        <v>30081009</v>
+        <v>30011009</v>
       </c>
       <c r="B13" s="25">
         <v>30</v>
       </c>
-      <c r="C13" s="25">
-        <v>8</v>
+      <c r="C13" s="32">
+        <v>1</v>
       </c>
       <c r="D13" s="25">
         <v>1009</v>
       </c>
       <c r="E13" s="24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" s="24">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <f t="shared" si="0"/>
-        <v>30091010</v>
+        <v>30001010</v>
       </c>
       <c r="B14" s="25">
         <v>30</v>
       </c>
-      <c r="C14" s="25">
-        <v>9</v>
+      <c r="C14" s="32">
+        <v>0</v>
       </c>
       <c r="D14" s="25">
         <v>1010</v>
       </c>
       <c r="E14" s="24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" s="24">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <f t="shared" si="0"/>
-        <v>30101011</v>
+        <v>30011011</v>
       </c>
       <c r="B15" s="25">
         <v>30</v>
       </c>
-      <c r="C15" s="25">
-        <v>10</v>
+      <c r="C15" s="32">
+        <v>1</v>
       </c>
       <c r="D15" s="25">
         <v>1011</v>
       </c>
       <c r="E15" s="24">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F15" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="34">
+        <v>0.7</v>
+      </c>
+      <c r="L15" s="27"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
         <f t="shared" si="0"/>
-        <v>30111012</v>
+        <v>30001012</v>
       </c>
       <c r="B16" s="25">
         <v>30</v>
       </c>
-      <c r="C16" s="25">
-        <v>11</v>
+      <c r="C16" s="32">
+        <v>0</v>
       </c>
       <c r="D16" s="25">
         <v>1012</v>
       </c>
       <c r="E16" s="24">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F16" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="34">
+        <v>1.3</v>
+      </c>
+      <c r="L16" s="27"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <f t="shared" si="0"/>
-        <v>30121013</v>
+        <v>30011013</v>
       </c>
       <c r="B17" s="25">
         <v>30</v>
       </c>
-      <c r="C17" s="25">
-        <v>12</v>
+      <c r="C17" s="32">
+        <v>1</v>
       </c>
       <c r="D17" s="25">
         <v>1013</v>
       </c>
       <c r="E17" s="24">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F17" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
         <f t="shared" si="0"/>
-        <v>30131014</v>
+        <v>30001014</v>
       </c>
       <c r="B18" s="25">
         <v>30</v>
       </c>
-      <c r="C18" s="25">
-        <v>13</v>
+      <c r="C18" s="32">
+        <v>0</v>
       </c>
       <c r="D18" s="25">
         <v>1014</v>
       </c>
       <c r="E18" s="24">
+        <v>8</v>
+      </c>
+      <c r="F18" s="24">
+        <v>1</v>
+      </c>
+      <c r="G18" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="25">
+        <f t="shared" si="0"/>
+        <v>30011015</v>
+      </c>
+      <c r="B19" s="25">
+        <v>30</v>
+      </c>
+      <c r="C19" s="32">
+        <v>1</v>
+      </c>
+      <c r="D19" s="25">
+        <v>1015</v>
+      </c>
+      <c r="E19" s="24">
+        <v>8</v>
+      </c>
+      <c r="F19" s="24">
+        <v>1</v>
+      </c>
+      <c r="G19" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="25">
+        <f t="shared" si="0"/>
+        <v>30001016</v>
+      </c>
+      <c r="B20" s="25">
+        <v>30</v>
+      </c>
+      <c r="C20" s="32">
+        <v>0</v>
+      </c>
+      <c r="D20" s="25">
+        <v>1016</v>
+      </c>
+      <c r="E20" s="24">
+        <v>9</v>
+      </c>
+      <c r="F20" s="24">
+        <v>1</v>
+      </c>
+      <c r="G20" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="25">
+        <f t="shared" ref="A21:A46" si="1">(B21*1000000) + (C21*10000) + D21</f>
+        <v>30011017</v>
+      </c>
+      <c r="B21" s="25">
+        <v>30</v>
+      </c>
+      <c r="C21" s="32">
+        <v>1</v>
+      </c>
+      <c r="D21" s="25">
+        <v>1017</v>
+      </c>
+      <c r="E21" s="24">
+        <v>9</v>
+      </c>
+      <c r="F21" s="24">
+        <v>1</v>
+      </c>
+      <c r="G21" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="25">
+        <f t="shared" si="1"/>
+        <v>30001018</v>
+      </c>
+      <c r="B22" s="25">
+        <v>30</v>
+      </c>
+      <c r="C22" s="32">
+        <v>0</v>
+      </c>
+      <c r="D22" s="25">
+        <v>1018</v>
+      </c>
+      <c r="E22" s="24">
+        <v>10</v>
+      </c>
+      <c r="F22" s="24">
+        <v>1</v>
+      </c>
+      <c r="G22" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="25">
+        <f t="shared" si="1"/>
+        <v>30011019</v>
+      </c>
+      <c r="B23" s="25">
+        <v>30</v>
+      </c>
+      <c r="C23" s="32">
+        <v>1</v>
+      </c>
+      <c r="D23" s="25">
+        <v>1019</v>
+      </c>
+      <c r="E23" s="24">
+        <v>10</v>
+      </c>
+      <c r="F23" s="24">
+        <v>1</v>
+      </c>
+      <c r="G23" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="25">
+        <f t="shared" si="1"/>
+        <v>30001020</v>
+      </c>
+      <c r="B24" s="25">
+        <v>30</v>
+      </c>
+      <c r="C24" s="32">
+        <v>0</v>
+      </c>
+      <c r="D24" s="25">
+        <v>1020</v>
+      </c>
+      <c r="E24" s="24">
+        <v>11</v>
+      </c>
+      <c r="F24" s="24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="25">
+        <f t="shared" si="1"/>
+        <v>30011021</v>
+      </c>
+      <c r="B25" s="25">
+        <v>30</v>
+      </c>
+      <c r="C25" s="32">
+        <v>1</v>
+      </c>
+      <c r="D25" s="25">
+        <v>1021</v>
+      </c>
+      <c r="E25" s="24">
+        <v>11</v>
+      </c>
+      <c r="F25" s="24">
+        <v>1</v>
+      </c>
+      <c r="G25" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="25">
+        <f t="shared" si="1"/>
+        <v>30001022</v>
+      </c>
+      <c r="B26" s="25">
+        <v>30</v>
+      </c>
+      <c r="C26" s="32">
+        <v>0</v>
+      </c>
+      <c r="D26" s="25">
+        <v>1022</v>
+      </c>
+      <c r="E26" s="24">
+        <v>12</v>
+      </c>
+      <c r="F26" s="24">
+        <v>1</v>
+      </c>
+      <c r="G26" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="25">
+        <f t="shared" si="1"/>
+        <v>30011023</v>
+      </c>
+      <c r="B27" s="25">
+        <v>30</v>
+      </c>
+      <c r="C27" s="32">
+        <v>1</v>
+      </c>
+      <c r="D27" s="25">
+        <v>1023</v>
+      </c>
+      <c r="E27" s="24">
+        <v>12</v>
+      </c>
+      <c r="F27" s="24">
+        <v>1</v>
+      </c>
+      <c r="G27" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="25">
+        <f t="shared" si="1"/>
+        <v>30001024</v>
+      </c>
+      <c r="B28" s="25">
+        <v>30</v>
+      </c>
+      <c r="C28" s="32">
+        <v>0</v>
+      </c>
+      <c r="D28" s="25">
+        <v>1024</v>
+      </c>
+      <c r="E28" s="24">
+        <v>13</v>
+      </c>
+      <c r="F28" s="24">
+        <v>1</v>
+      </c>
+      <c r="G28" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="25">
+        <f t="shared" si="1"/>
+        <v>30011025</v>
+      </c>
+      <c r="B29" s="25">
+        <v>30</v>
+      </c>
+      <c r="C29" s="32">
+        <v>1</v>
+      </c>
+      <c r="D29" s="25">
+        <v>1025</v>
+      </c>
+      <c r="E29" s="24">
+        <v>13</v>
+      </c>
+      <c r="F29" s="24">
+        <v>1</v>
+      </c>
+      <c r="G29" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="25">
+        <f t="shared" si="1"/>
+        <v>30001026</v>
+      </c>
+      <c r="B30" s="25">
+        <v>30</v>
+      </c>
+      <c r="C30" s="32">
+        <v>0</v>
+      </c>
+      <c r="D30" s="25">
+        <v>1026</v>
+      </c>
+      <c r="E30" s="24">
         <v>14</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F30" s="24">
+        <v>1</v>
+      </c>
+      <c r="G30" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="25">
+        <f>(B31*1000000) + (C32*10000) + D31</f>
+        <v>30001027</v>
+      </c>
+      <c r="B31" s="25">
+        <v>30</v>
+      </c>
+      <c r="C31" s="32">
+        <v>1</v>
+      </c>
+      <c r="D31" s="25">
+        <v>1027</v>
+      </c>
+      <c r="E31" s="24">
+        <v>14</v>
+      </c>
+      <c r="F31" s="24">
+        <v>1</v>
+      </c>
+      <c r="G31" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="25">
+        <f>(B32*1000000) + (C33*10000) + D32</f>
+        <v>30011028</v>
+      </c>
+      <c r="B32" s="25">
+        <v>30</v>
+      </c>
+      <c r="C32" s="32">
+        <v>0</v>
+      </c>
+      <c r="D32" s="25">
+        <v>1028</v>
+      </c>
+      <c r="E32" s="24">
+        <v>15</v>
+      </c>
+      <c r="F32" s="24">
+        <v>1</v>
+      </c>
+      <c r="G32" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="25">
+        <f>(B33*1000000) + (C34*10000) + D33</f>
+        <v>30001029</v>
+      </c>
+      <c r="B33" s="25">
+        <v>30</v>
+      </c>
+      <c r="C33" s="32">
+        <v>1</v>
+      </c>
+      <c r="D33" s="25">
+        <v>1029</v>
+      </c>
+      <c r="E33" s="24">
+        <v>15</v>
+      </c>
+      <c r="F33" s="24">
+        <v>1</v>
+      </c>
+      <c r="G33" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="25">
+        <f>(B34*1000000) + (C35*10000) + D34</f>
+        <v>30011030</v>
+      </c>
+      <c r="B34" s="25">
+        <v>30</v>
+      </c>
+      <c r="C34" s="32">
+        <v>0</v>
+      </c>
+      <c r="D34" s="25">
+        <v>1030</v>
+      </c>
+      <c r="E34" s="24">
+        <v>16</v>
+      </c>
+      <c r="F34" s="24">
+        <v>1</v>
+      </c>
+      <c r="G34" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="25">
+        <f>(B35*1000000) + (C36*10000) + D35</f>
+        <v>30001031</v>
+      </c>
+      <c r="B35" s="25">
+        <v>30</v>
+      </c>
+      <c r="C35" s="32">
+        <v>1</v>
+      </c>
+      <c r="D35" s="25">
+        <v>1031</v>
+      </c>
+      <c r="E35" s="24">
+        <v>16</v>
+      </c>
+      <c r="F35" s="24">
+        <v>1</v>
+      </c>
+      <c r="G35" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="25">
+        <f>(B36*1000000) + (C37*10000) + D36</f>
+        <v>30011032</v>
+      </c>
+      <c r="B36" s="25">
+        <v>30</v>
+      </c>
+      <c r="C36" s="32">
+        <v>0</v>
+      </c>
+      <c r="D36" s="25">
+        <v>1032</v>
+      </c>
+      <c r="E36" s="24">
+        <v>17</v>
+      </c>
+      <c r="F36" s="24">
+        <v>1</v>
+      </c>
+      <c r="G36" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="25">
+        <f>(B37*1000000) + (C38*10000) + D37</f>
+        <v>30001033</v>
+      </c>
+      <c r="B37" s="25">
+        <v>30</v>
+      </c>
+      <c r="C37" s="32">
+        <v>1</v>
+      </c>
+      <c r="D37" s="25">
+        <v>1033</v>
+      </c>
+      <c r="E37" s="24">
+        <v>17</v>
+      </c>
+      <c r="F37" s="24">
+        <v>1</v>
+      </c>
+      <c r="G37" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="25">
+        <f>(B38*1000000) + (C39*10000) + D38</f>
+        <v>30011034</v>
+      </c>
+      <c r="B38" s="25">
+        <v>30</v>
+      </c>
+      <c r="C38" s="32">
+        <v>0</v>
+      </c>
+      <c r="D38" s="25">
+        <v>1034</v>
+      </c>
+      <c r="E38" s="24">
+        <v>18</v>
+      </c>
+      <c r="F38" s="24">
+        <v>1</v>
+      </c>
+      <c r="G38" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="25">
+        <f>(B39*1000000) + (C40*10000) + D39</f>
+        <v>30001035</v>
+      </c>
+      <c r="B39" s="25">
+        <v>30</v>
+      </c>
+      <c r="C39" s="32">
+        <v>1</v>
+      </c>
+      <c r="D39" s="25">
+        <v>1035</v>
+      </c>
+      <c r="E39" s="24">
+        <v>18</v>
+      </c>
+      <c r="F39" s="24">
+        <v>1</v>
+      </c>
+      <c r="G39" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="25">
+        <f>(B40*1000000) + (C41*10000) + D40</f>
+        <v>30011036</v>
+      </c>
+      <c r="B40" s="25">
+        <v>30</v>
+      </c>
+      <c r="C40" s="32">
+        <v>0</v>
+      </c>
+      <c r="D40" s="25">
+        <v>1036</v>
+      </c>
+      <c r="E40" s="24">
+        <v>19</v>
+      </c>
+      <c r="F40" s="24">
+        <v>1</v>
+      </c>
+      <c r="G40" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="25">
+        <f>(B41*1000000) + (C42*10000) + D41</f>
+        <v>30001037</v>
+      </c>
+      <c r="B41" s="25">
+        <v>30</v>
+      </c>
+      <c r="C41" s="32">
+        <v>1</v>
+      </c>
+      <c r="D41" s="25">
+        <v>1037</v>
+      </c>
+      <c r="E41" s="24">
+        <v>19</v>
+      </c>
+      <c r="F41" s="24">
+        <v>1</v>
+      </c>
+      <c r="G41" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="25">
+        <f>(B42*1000000) + (C43*10000) + D42</f>
+        <v>30011038</v>
+      </c>
+      <c r="B42" s="25">
+        <v>30</v>
+      </c>
+      <c r="C42" s="32">
+        <v>0</v>
+      </c>
+      <c r="D42" s="25">
+        <v>1038</v>
+      </c>
+      <c r="E42" s="24">
+        <v>20</v>
+      </c>
+      <c r="F42" s="24">
+        <v>1</v>
+      </c>
+      <c r="G42" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="25">
+        <f>(B43*1000000) + (C44*10000) + D43</f>
+        <v>30011039</v>
+      </c>
+      <c r="B43" s="25">
+        <v>30</v>
+      </c>
+      <c r="C43" s="32">
+        <v>1</v>
+      </c>
+      <c r="D43" s="25">
+        <v>1039</v>
+      </c>
+      <c r="E43" s="24">
+        <v>20</v>
+      </c>
+      <c r="F43" s="24">
+        <v>1</v>
+      </c>
+      <c r="G43" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="25">
+        <f>(B44*1000000) + (C45*10000) + D44</f>
+        <v>30001040</v>
+      </c>
+      <c r="B44" s="25">
+        <v>30</v>
+      </c>
+      <c r="C44" s="32">
+        <v>1</v>
+      </c>
+      <c r="D44" s="25">
+        <v>1040</v>
+      </c>
+      <c r="E44" s="24">
+        <v>21</v>
+      </c>
+      <c r="F44" s="24">
+        <v>1</v>
+      </c>
+      <c r="G44" s="34">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="25">
+        <f>(B45*1000000) + (C46*10000) + D45</f>
+        <v>30011041</v>
+      </c>
+      <c r="B45" s="25">
+        <v>30</v>
+      </c>
+      <c r="C45" s="32">
+        <v>0</v>
+      </c>
+      <c r="D45" s="25">
+        <v>1041</v>
+      </c>
+      <c r="E45" s="24">
+        <v>22</v>
+      </c>
+      <c r="F45" s="24">
+        <v>1</v>
+      </c>
+      <c r="G45" s="34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="25">
+        <f>(B46*1000000) + (C47*10000) + D46</f>
+        <v>30001042</v>
+      </c>
+      <c r="B46" s="25">
+        <v>30</v>
+      </c>
+      <c r="C46" s="32">
+        <v>1</v>
+      </c>
+      <c r="D46" s="25">
+        <v>1042</v>
+      </c>
+      <c r="E46" s="24">
+        <v>23</v>
+      </c>
+      <c r="F46" s="24">
+        <v>2</v>
+      </c>
+      <c r="G46" s="34">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="25">
+        <f>(B47*1000000) + (C48*10000) + D47</f>
+        <v>30001043</v>
+      </c>
+      <c r="B47" s="25">
+        <v>30</v>
+      </c>
+      <c r="C47" s="32">
+        <v>0</v>
+      </c>
+      <c r="D47" s="25">
+        <v>1043</v>
+      </c>
+      <c r="E47" s="24">
+        <v>24</v>
+      </c>
+      <c r="F47" s="24">
+        <v>0</v>
+      </c>
+      <c r="G47" s="34">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1048576" xr:uid="{95F9219A-BB1D-427C-A5C7-0F9EDA01E71B}">
+  <conditionalFormatting sqref="C1:C1048576 C1:C4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color theme="8" tint="0.59999389629810485"/>
+        <color rgb="FFFFA7A7"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5 F7 F9:F10 F12 F14 F16 F19 F21 F23 F25 F27 F29 F32:F1048576" xr:uid="{95F9219A-BB1D-427C-A5C7-0F9EDA01E71B}">
       <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C30 C32:C1048576" xr:uid="{2E37FA97-16C9-4CD8-BF57-92BA0291CA83}">
+      <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Data/DataTable/03_Buf_Table.xlsx
+++ b/Assets/Data/DataTable/03_Buf_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4174B785-3716-44A7-AC4F-5F0653E8D75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28201E6-C58E-4299-AB29-8C3CEF480FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -465,7 +465,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -818,6 +818,10 @@
   </si>
   <si>
     <t>Buf_Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buf_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -827,8 +831,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="00"/>
-    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="00"/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1068,16 +1072,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3813,7 +3817,7 @@
     </row>
     <row r="4" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>59</v>
@@ -4223,7 +4227,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
-        <f t="shared" ref="A21:A46" si="1">(B21*1000000) + (C21*10000) + D21</f>
+        <f t="shared" ref="A21:A30" si="1">(B21*1000000) + (C21*10000) + D21</f>
         <v>30011017</v>
       </c>
       <c r="B21" s="25">
@@ -4463,7 +4467,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="25">
-        <f>(B31*1000000) + (C32*10000) + D31</f>
+        <f t="shared" ref="A31:A47" si="2">(B31*1000000) + (C32*10000) + D31</f>
         <v>30001027</v>
       </c>
       <c r="B31" s="25">
@@ -4487,7 +4491,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="25">
-        <f>(B32*1000000) + (C33*10000) + D32</f>
+        <f t="shared" si="2"/>
         <v>30011028</v>
       </c>
       <c r="B32" s="25">
@@ -4511,7 +4515,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="25">
-        <f>(B33*1000000) + (C34*10000) + D33</f>
+        <f t="shared" si="2"/>
         <v>30001029</v>
       </c>
       <c r="B33" s="25">
@@ -4535,7 +4539,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="25">
-        <f>(B34*1000000) + (C35*10000) + D34</f>
+        <f t="shared" si="2"/>
         <v>30011030</v>
       </c>
       <c r="B34" s="25">
@@ -4559,7 +4563,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="25">
-        <f>(B35*1000000) + (C36*10000) + D35</f>
+        <f t="shared" si="2"/>
         <v>30001031</v>
       </c>
       <c r="B35" s="25">
@@ -4583,7 +4587,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="25">
-        <f>(B36*1000000) + (C37*10000) + D36</f>
+        <f t="shared" si="2"/>
         <v>30011032</v>
       </c>
       <c r="B36" s="25">
@@ -4607,7 +4611,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="25">
-        <f>(B37*1000000) + (C38*10000) + D37</f>
+        <f t="shared" si="2"/>
         <v>30001033</v>
       </c>
       <c r="B37" s="25">
@@ -4631,7 +4635,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="25">
-        <f>(B38*1000000) + (C39*10000) + D38</f>
+        <f t="shared" si="2"/>
         <v>30011034</v>
       </c>
       <c r="B38" s="25">
@@ -4655,7 +4659,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="25">
-        <f>(B39*1000000) + (C40*10000) + D39</f>
+        <f t="shared" si="2"/>
         <v>30001035</v>
       </c>
       <c r="B39" s="25">
@@ -4679,7 +4683,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="25">
-        <f>(B40*1000000) + (C41*10000) + D40</f>
+        <f t="shared" si="2"/>
         <v>30011036</v>
       </c>
       <c r="B40" s="25">
@@ -4703,7 +4707,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="25">
-        <f>(B41*1000000) + (C42*10000) + D41</f>
+        <f t="shared" si="2"/>
         <v>30001037</v>
       </c>
       <c r="B41" s="25">
@@ -4727,7 +4731,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="25">
-        <f>(B42*1000000) + (C43*10000) + D42</f>
+        <f t="shared" si="2"/>
         <v>30011038</v>
       </c>
       <c r="B42" s="25">
@@ -4751,7 +4755,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="25">
-        <f>(B43*1000000) + (C44*10000) + D43</f>
+        <f t="shared" si="2"/>
         <v>30011039</v>
       </c>
       <c r="B43" s="25">
@@ -4775,7 +4779,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="25">
-        <f>(B44*1000000) + (C45*10000) + D44</f>
+        <f t="shared" si="2"/>
         <v>30001040</v>
       </c>
       <c r="B44" s="25">
@@ -4799,7 +4803,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="25">
-        <f>(B45*1000000) + (C46*10000) + D45</f>
+        <f t="shared" si="2"/>
         <v>30011041</v>
       </c>
       <c r="B45" s="25">
@@ -4823,7 +4827,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="25">
-        <f>(B46*1000000) + (C47*10000) + D46</f>
+        <f t="shared" si="2"/>
         <v>30001042</v>
       </c>
       <c r="B46" s="25">
@@ -4847,7 +4851,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="25">
-        <f>(B47*1000000) + (C48*10000) + D47</f>
+        <f t="shared" si="2"/>
         <v>30001043</v>
       </c>
       <c r="B47" s="25">

--- a/Assets/Data/DataTable/03_Buf_Table.xlsx
+++ b/Assets/Data/DataTable/03_Buf_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28201E6-C58E-4299-AB29-8C3CEF480FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4780B0F1-B11D-460F-AF9E-E8E1A6F7A179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -354,10 +354,21 @@
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>종류에</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">0: </t>
+          <t xml:space="preserve"> </t>
         </r>
         <r>
           <rPr>
@@ -368,8 +379,7 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t xml:space="preserve">버프
-</t>
+          <t>상관없이</t>
         </r>
         <r>
           <rPr>
@@ -379,7 +389,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">1: </t>
+          <t xml:space="preserve"> 00</t>
         </r>
         <r>
           <rPr>
@@ -390,7 +400,28 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>디버프</t>
+          <t>으로</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
         </r>
       </text>
     </comment>
@@ -406,57 +437,31 @@
             <charset val="129"/>
           </rPr>
           <t>0: NONE
-1: 공격력
-2: 방어력
-3: SP 보유량
-4: 스피드
-5: 치명타 확률
-6: 치명타 데미지 배율
-7: 카운터 데미지 배율
-8: 물리 속성 게이지 효율 계수
-9: 화염 속성 게이지 효율 계수
-10: 방사능 속성 게이지 효율 계수
-11: 중력 속성 게이지 효율 계수
-12: 공허 속성 게이지 효율 계수
-13: 신성 속성 게이지 효율 계수
-14: 속성 게이지 저항 계수
-15: 물리 속성 과부하 계수
-16: 화염 속성 과부하 계수
-17: 방사능 속성 과부하 계수
-18: 중력 속성 과부하 계수
-19: 공허 속성 과부하 계수
-20: 신성 속성 과부하 계수
-21: 받는 피해 증가
-22: 받는 피해 감소
-23: SP 소모량 증가
-24: 도발</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{A004C954-977A-4174-878C-4EC4F25E7E59}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0: NONE
-1: Add </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-2: Mul
-3: Override</t>
+1: Max_HP
+2: Max_SP
+3: Attack
+4: Defense
+5: Speed
+6: Critical Chance
+7: Critical Damage Rate
+8: Counter Damage Rate
+9: 물리 속성 게이지 효율 계수
+10: 화염 속성 게이지 효율 계수
+11: 방사능 속성 게이지 효율 계수
+12: 중력 속성 게이지 효율 계수
+13: 공허 속성 게이지 효율 계수
+14: 신성 속성 게이지 효율 계수
+15: 속성 게이지 저항 계수
+16: 물리 속성 과부하 계수
+17: 화염 속성 과부하 계수
+18: 방사능 속성 과부하 계수
+19: 중력 속성 과부하 계수
+20: 공허 속성 과부하 계수
+21: 신성 속성 과부하 계수
+22: 피해 배율
+23: 받는 피해 배율
+24: SP 소모량 증가
+25: 도발</t>
         </r>
       </text>
     </comment>
@@ -465,7 +470,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -784,21 +789,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enum:Buf_Category:NONE</t>
-  </si>
-  <si>
-    <t>enum:Buf_Category:NONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">보정 방식 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>enum:Calculate_Mode</t>
-  </si>
-  <si>
-    <t>enum:Calculate_Mode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -806,22 +797,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Calculate_Mode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보정 수치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>Buf_Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Buf_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:BUFF_TYPE:NONE</t>
+  </si>
+  <si>
+    <t>enum:BUFF_TYPE:NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3384,7 +3375,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
@@ -3392,11 +3383,14 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
         <v>73</v>
       </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
@@ -3745,7 +3739,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" style="30" bestFit="1" customWidth="1"/>
@@ -3753,11 +3747,10 @@
     <col min="3" max="3" width="13.875" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.625" style="31" customWidth="1"/>
-    <col min="6" max="6" width="19.375" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.125" style="35" customWidth="1"/>
+    <col min="6" max="6" width="22.125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -3766,9 +3759,8 @@
       <c r="D1"/>
       <c r="E1"/>
       <c r="F1"/>
-      <c r="G1"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>77</v>
       </c>
@@ -3784,14 +3776,9 @@
       <c r="E2" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="22"/>
+    </row>
+    <row r="3" spans="1:12" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>70</v>
       </c>
@@ -3805,19 +3792,14 @@
         <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="M3"/>
-    </row>
-    <row r="4" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="29"/>
+      <c r="L3"/>
+    </row>
+    <row r="4" spans="1:12" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>59</v>
@@ -3829,17 +3811,12 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="M4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="L4"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>30001001</v>
@@ -3856,38 +3833,28 @@
       <c r="E5" s="24">
         <v>1</v>
       </c>
-      <c r="F5" s="24">
-        <v>2</v>
-      </c>
-      <c r="G5" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F5" s="34"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <f>(B6*1000000) + (C6*10000) + D6</f>
-        <v>30011002</v>
+        <v>30001002</v>
       </c>
       <c r="B6" s="25">
         <v>30</v>
       </c>
       <c r="C6" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="25">
         <v>1002</v>
       </c>
       <c r="E6" s="24">
-        <v>1</v>
-      </c>
-      <c r="F6" s="24">
         <v>2</v>
       </c>
-      <c r="G6" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F6" s="34"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <f t="shared" ref="A7:A20" si="0">(B7*1000000) + (C7*10000) + D7</f>
         <v>30001003</v>
@@ -3902,40 +3869,30 @@
         <v>1003</v>
       </c>
       <c r="E7" s="24">
-        <v>2</v>
-      </c>
-      <c r="F7" s="24">
-        <v>2</v>
-      </c>
-      <c r="G7" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="F7" s="34"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <f t="shared" si="0"/>
-        <v>30011004</v>
+        <v>30001004</v>
       </c>
       <c r="B8" s="25">
         <v>30</v>
       </c>
       <c r="C8" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="25">
         <v>1004</v>
       </c>
       <c r="E8" s="24">
-        <v>2</v>
-      </c>
-      <c r="F8" s="24">
-        <v>2</v>
-      </c>
-      <c r="G8" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="F8" s="34"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <f t="shared" si="0"/>
         <v>30001005</v>
@@ -3950,16 +3907,11 @@
         <v>1005</v>
       </c>
       <c r="E9" s="24">
-        <v>3</v>
-      </c>
-      <c r="F9" s="24">
-        <v>1</v>
-      </c>
-      <c r="G9" s="34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <f t="shared" si="0"/>
         <v>30001006</v>
@@ -3974,40 +3926,30 @@
         <v>1006</v>
       </c>
       <c r="E10" s="24">
-        <v>4</v>
-      </c>
-      <c r="F10" s="24">
-        <v>2</v>
-      </c>
-      <c r="G10" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <f t="shared" si="0"/>
-        <v>30011007</v>
+        <v>30001007</v>
       </c>
       <c r="B11" s="25">
         <v>30</v>
       </c>
       <c r="C11" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="25">
         <v>1007</v>
       </c>
       <c r="E11" s="24">
-        <v>4</v>
-      </c>
-      <c r="F11" s="24">
-        <v>2</v>
-      </c>
-      <c r="G11" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F11" s="34"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <f t="shared" si="0"/>
         <v>30001008</v>
@@ -4022,40 +3964,30 @@
         <v>1008</v>
       </c>
       <c r="E12" s="24">
-        <v>5</v>
-      </c>
-      <c r="F12" s="24">
-        <v>1</v>
-      </c>
-      <c r="G12" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F12" s="34"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <f t="shared" si="0"/>
-        <v>30011009</v>
+        <v>30001009</v>
       </c>
       <c r="B13" s="25">
         <v>30</v>
       </c>
       <c r="C13" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="25">
         <v>1009</v>
       </c>
       <c r="E13" s="24">
-        <v>5</v>
-      </c>
-      <c r="F13" s="24">
-        <v>1</v>
-      </c>
-      <c r="G13" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="F13" s="34"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <f t="shared" si="0"/>
         <v>30001010</v>
@@ -4070,41 +4002,31 @@
         <v>1010</v>
       </c>
       <c r="E14" s="24">
-        <v>6</v>
-      </c>
-      <c r="F14" s="24">
-        <v>1</v>
-      </c>
-      <c r="G14" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="F14" s="34"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <f t="shared" si="0"/>
-        <v>30011011</v>
+        <v>30001011</v>
       </c>
       <c r="B15" s="25">
         <v>30</v>
       </c>
       <c r="C15" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="25">
         <v>1011</v>
       </c>
       <c r="E15" s="24">
-        <v>6</v>
-      </c>
-      <c r="F15" s="24">
-        <v>1</v>
-      </c>
-      <c r="G15" s="34">
-        <v>0.7</v>
-      </c>
-      <c r="L15" s="27"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
         <f t="shared" si="0"/>
         <v>30001012</v>
@@ -4119,41 +4041,31 @@
         <v>1012</v>
       </c>
       <c r="E16" s="24">
-        <v>7</v>
-      </c>
-      <c r="F16" s="24">
-        <v>1</v>
-      </c>
-      <c r="G16" s="34">
-        <v>1.3</v>
-      </c>
-      <c r="L16" s="27"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <f t="shared" si="0"/>
-        <v>30011013</v>
+        <v>30001013</v>
       </c>
       <c r="B17" s="25">
         <v>30</v>
       </c>
       <c r="C17" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="25">
         <v>1013</v>
       </c>
       <c r="E17" s="24">
-        <v>7</v>
-      </c>
-      <c r="F17" s="24">
-        <v>1</v>
-      </c>
-      <c r="G17" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="F17" s="34"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
         <f t="shared" si="0"/>
         <v>30001014</v>
@@ -4168,40 +4080,30 @@
         <v>1014</v>
       </c>
       <c r="E18" s="24">
-        <v>8</v>
-      </c>
-      <c r="F18" s="24">
-        <v>1</v>
-      </c>
-      <c r="G18" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="F18" s="34"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
         <f t="shared" si="0"/>
-        <v>30011015</v>
+        <v>30001015</v>
       </c>
       <c r="B19" s="25">
         <v>30</v>
       </c>
       <c r="C19" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="25">
         <v>1015</v>
       </c>
       <c r="E19" s="24">
-        <v>8</v>
-      </c>
-      <c r="F19" s="24">
-        <v>1</v>
-      </c>
-      <c r="G19" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="F19" s="34"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
         <f t="shared" si="0"/>
         <v>30001016</v>
@@ -4216,40 +4118,30 @@
         <v>1016</v>
       </c>
       <c r="E20" s="24">
-        <v>9</v>
-      </c>
-      <c r="F20" s="24">
-        <v>1</v>
-      </c>
-      <c r="G20" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="F20" s="34"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
         <f t="shared" ref="A21:A30" si="1">(B21*1000000) + (C21*10000) + D21</f>
-        <v>30011017</v>
+        <v>30001017</v>
       </c>
       <c r="B21" s="25">
         <v>30</v>
       </c>
       <c r="C21" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="25">
         <v>1017</v>
       </c>
       <c r="E21" s="24">
-        <v>9</v>
-      </c>
-      <c r="F21" s="24">
-        <v>1</v>
-      </c>
-      <c r="G21" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="F21" s="34"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
         <f t="shared" si="1"/>
         <v>30001018</v>
@@ -4264,40 +4156,30 @@
         <v>1018</v>
       </c>
       <c r="E22" s="24">
-        <v>10</v>
-      </c>
-      <c r="F22" s="24">
-        <v>1</v>
-      </c>
-      <c r="G22" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="F22" s="34"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="25">
         <f t="shared" si="1"/>
-        <v>30011019</v>
+        <v>30001019</v>
       </c>
       <c r="B23" s="25">
         <v>30</v>
       </c>
       <c r="C23" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="25">
         <v>1019</v>
       </c>
       <c r="E23" s="24">
-        <v>10</v>
-      </c>
-      <c r="F23" s="24">
-        <v>1</v>
-      </c>
-      <c r="G23" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="F23" s="34"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="25">
         <f t="shared" si="1"/>
         <v>30001020</v>
@@ -4312,40 +4194,30 @@
         <v>1020</v>
       </c>
       <c r="E24" s="24">
-        <v>11</v>
-      </c>
-      <c r="F24" s="24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="F24" s="34"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="25">
         <f t="shared" si="1"/>
-        <v>30011021</v>
+        <v>30001021</v>
       </c>
       <c r="B25" s="25">
         <v>30</v>
       </c>
       <c r="C25" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="25">
         <v>1021</v>
       </c>
       <c r="E25" s="24">
-        <v>11</v>
-      </c>
-      <c r="F25" s="24">
-        <v>1</v>
-      </c>
-      <c r="G25" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="F25" s="34"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="25">
         <f t="shared" si="1"/>
         <v>30001022</v>
@@ -4360,40 +4232,30 @@
         <v>1022</v>
       </c>
       <c r="E26" s="24">
-        <v>12</v>
-      </c>
-      <c r="F26" s="24">
-        <v>1</v>
-      </c>
-      <c r="G26" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="F26" s="34"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="25">
         <f t="shared" si="1"/>
-        <v>30011023</v>
+        <v>30001023</v>
       </c>
       <c r="B27" s="25">
         <v>30</v>
       </c>
       <c r="C27" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="25">
         <v>1023</v>
       </c>
       <c r="E27" s="24">
-        <v>12</v>
-      </c>
-      <c r="F27" s="24">
-        <v>1</v>
-      </c>
-      <c r="G27" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="F27" s="34"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="25">
         <f t="shared" si="1"/>
         <v>30001024</v>
@@ -4408,468 +4270,134 @@
         <v>1024</v>
       </c>
       <c r="E28" s="24">
-        <v>13</v>
-      </c>
-      <c r="F28" s="24">
-        <v>1</v>
-      </c>
-      <c r="G28" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="F28" s="34"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="25">
         <f t="shared" si="1"/>
-        <v>30011025</v>
-      </c>
-      <c r="B29" s="25">
-        <v>30</v>
+        <v>30001025</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>88</v>
       </c>
       <c r="C29" s="32">
-        <v>1</v>
-      </c>
-      <c r="D29" s="25">
-        <v>1025</v>
+        <v>0</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>89</v>
       </c>
       <c r="E29" s="24">
-        <v>13</v>
-      </c>
-      <c r="F29" s="24">
-        <v>1</v>
-      </c>
-      <c r="G29" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="25">
+        <v>25</v>
+      </c>
+      <c r="F29" s="34"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="30">
         <f t="shared" si="1"/>
-        <v>30001026</v>
-      </c>
-      <c r="B30" s="25">
-        <v>30</v>
-      </c>
-      <c r="C30" s="32">
-        <v>0</v>
-      </c>
-      <c r="D30" s="25">
-        <v>1026</v>
-      </c>
-      <c r="E30" s="24">
-        <v>14</v>
-      </c>
-      <c r="F30" s="24">
-        <v>1</v>
-      </c>
-      <c r="G30" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="30">
         <f t="shared" ref="A31:A47" si="2">(B31*1000000) + (C32*10000) + D31</f>
-        <v>30001027</v>
-      </c>
-      <c r="B31" s="25">
-        <v>30</v>
-      </c>
-      <c r="C31" s="32">
-        <v>1</v>
-      </c>
-      <c r="D31" s="25">
-        <v>1027</v>
-      </c>
-      <c r="E31" s="24">
-        <v>14</v>
-      </c>
-      <c r="F31" s="24">
-        <v>1</v>
-      </c>
-      <c r="G31" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="30">
         <f t="shared" si="2"/>
-        <v>30011028</v>
-      </c>
-      <c r="B32" s="25">
-        <v>30</v>
-      </c>
-      <c r="C32" s="32">
-        <v>0</v>
-      </c>
-      <c r="D32" s="25">
-        <v>1028</v>
-      </c>
-      <c r="E32" s="24">
-        <v>15</v>
-      </c>
-      <c r="F32" s="24">
-        <v>1</v>
-      </c>
-      <c r="G32" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="30">
         <f t="shared" si="2"/>
-        <v>30001029</v>
-      </c>
-      <c r="B33" s="25">
-        <v>30</v>
-      </c>
-      <c r="C33" s="32">
-        <v>1</v>
-      </c>
-      <c r="D33" s="25">
-        <v>1029</v>
-      </c>
-      <c r="E33" s="24">
-        <v>15</v>
-      </c>
-      <c r="F33" s="24">
-        <v>1</v>
-      </c>
-      <c r="G33" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="30">
         <f t="shared" si="2"/>
-        <v>30011030</v>
-      </c>
-      <c r="B34" s="25">
-        <v>30</v>
-      </c>
-      <c r="C34" s="32">
-        <v>0</v>
-      </c>
-      <c r="D34" s="25">
-        <v>1030</v>
-      </c>
-      <c r="E34" s="24">
-        <v>16</v>
-      </c>
-      <c r="F34" s="24">
-        <v>1</v>
-      </c>
-      <c r="G34" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="30">
         <f t="shared" si="2"/>
-        <v>30001031</v>
-      </c>
-      <c r="B35" s="25">
-        <v>30</v>
-      </c>
-      <c r="C35" s="32">
-        <v>1</v>
-      </c>
-      <c r="D35" s="25">
-        <v>1031</v>
-      </c>
-      <c r="E35" s="24">
-        <v>16</v>
-      </c>
-      <c r="F35" s="24">
-        <v>1</v>
-      </c>
-      <c r="G35" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="30">
         <f t="shared" si="2"/>
-        <v>30011032</v>
-      </c>
-      <c r="B36" s="25">
-        <v>30</v>
-      </c>
-      <c r="C36" s="32">
-        <v>0</v>
-      </c>
-      <c r="D36" s="25">
-        <v>1032</v>
-      </c>
-      <c r="E36" s="24">
-        <v>17</v>
-      </c>
-      <c r="F36" s="24">
-        <v>1</v>
-      </c>
-      <c r="G36" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="30">
         <f t="shared" si="2"/>
-        <v>30001033</v>
-      </c>
-      <c r="B37" s="25">
-        <v>30</v>
-      </c>
-      <c r="C37" s="32">
-        <v>1</v>
-      </c>
-      <c r="D37" s="25">
-        <v>1033</v>
-      </c>
-      <c r="E37" s="24">
-        <v>17</v>
-      </c>
-      <c r="F37" s="24">
-        <v>1</v>
-      </c>
-      <c r="G37" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="30">
         <f t="shared" si="2"/>
-        <v>30011034</v>
-      </c>
-      <c r="B38" s="25">
-        <v>30</v>
-      </c>
-      <c r="C38" s="32">
-        <v>0</v>
-      </c>
-      <c r="D38" s="25">
-        <v>1034</v>
-      </c>
-      <c r="E38" s="24">
-        <v>18</v>
-      </c>
-      <c r="F38" s="24">
-        <v>1</v>
-      </c>
-      <c r="G38" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="30">
         <f t="shared" si="2"/>
-        <v>30001035</v>
-      </c>
-      <c r="B39" s="25">
-        <v>30</v>
-      </c>
-      <c r="C39" s="32">
-        <v>1</v>
-      </c>
-      <c r="D39" s="25">
-        <v>1035</v>
-      </c>
-      <c r="E39" s="24">
-        <v>18</v>
-      </c>
-      <c r="F39" s="24">
-        <v>1</v>
-      </c>
-      <c r="G39" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="30">
         <f t="shared" si="2"/>
-        <v>30011036</v>
-      </c>
-      <c r="B40" s="25">
-        <v>30</v>
-      </c>
-      <c r="C40" s="32">
-        <v>0</v>
-      </c>
-      <c r="D40" s="25">
-        <v>1036</v>
-      </c>
-      <c r="E40" s="24">
-        <v>19</v>
-      </c>
-      <c r="F40" s="24">
-        <v>1</v>
-      </c>
-      <c r="G40" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="30">
         <f t="shared" si="2"/>
-        <v>30001037</v>
-      </c>
-      <c r="B41" s="25">
-        <v>30</v>
-      </c>
-      <c r="C41" s="32">
-        <v>1</v>
-      </c>
-      <c r="D41" s="25">
-        <v>1037</v>
-      </c>
-      <c r="E41" s="24">
-        <v>19</v>
-      </c>
-      <c r="F41" s="24">
-        <v>1</v>
-      </c>
-      <c r="G41" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="30">
         <f t="shared" si="2"/>
-        <v>30011038</v>
-      </c>
-      <c r="B42" s="25">
-        <v>30</v>
-      </c>
-      <c r="C42" s="32">
-        <v>0</v>
-      </c>
-      <c r="D42" s="25">
-        <v>1038</v>
-      </c>
-      <c r="E42" s="24">
-        <v>20</v>
-      </c>
-      <c r="F42" s="24">
-        <v>1</v>
-      </c>
-      <c r="G42" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="30">
         <f t="shared" si="2"/>
-        <v>30011039</v>
-      </c>
-      <c r="B43" s="25">
-        <v>30</v>
-      </c>
-      <c r="C43" s="32">
-        <v>1</v>
-      </c>
-      <c r="D43" s="25">
-        <v>1039</v>
-      </c>
-      <c r="E43" s="24">
-        <v>20</v>
-      </c>
-      <c r="F43" s="24">
-        <v>1</v>
-      </c>
-      <c r="G43" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="30">
         <f t="shared" si="2"/>
-        <v>30001040</v>
-      </c>
-      <c r="B44" s="25">
-        <v>30</v>
-      </c>
-      <c r="C44" s="32">
-        <v>1</v>
-      </c>
-      <c r="D44" s="25">
-        <v>1040</v>
-      </c>
-      <c r="E44" s="24">
-        <v>21</v>
-      </c>
-      <c r="F44" s="24">
-        <v>1</v>
-      </c>
-      <c r="G44" s="34">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="30">
         <f t="shared" si="2"/>
-        <v>30011041</v>
-      </c>
-      <c r="B45" s="25">
-        <v>30</v>
-      </c>
-      <c r="C45" s="32">
-        <v>0</v>
-      </c>
-      <c r="D45" s="25">
-        <v>1041</v>
-      </c>
-      <c r="E45" s="24">
-        <v>22</v>
-      </c>
-      <c r="F45" s="24">
-        <v>1</v>
-      </c>
-      <c r="G45" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="30">
         <f t="shared" si="2"/>
-        <v>30001042</v>
-      </c>
-      <c r="B46" s="25">
-        <v>30</v>
-      </c>
-      <c r="C46" s="32">
-        <v>1</v>
-      </c>
-      <c r="D46" s="25">
-        <v>1042</v>
-      </c>
-      <c r="E46" s="24">
-        <v>23</v>
-      </c>
-      <c r="F46" s="24">
-        <v>2</v>
-      </c>
-      <c r="G46" s="34">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="30">
         <f t="shared" si="2"/>
-        <v>30001043</v>
-      </c>
-      <c r="B47" s="25">
-        <v>30</v>
-      </c>
-      <c r="C47" s="32">
-        <v>0</v>
-      </c>
-      <c r="D47" s="25">
-        <v>1043</v>
-      </c>
-      <c r="E47" s="24">
-        <v>24</v>
-      </c>
-      <c r="F47" s="24">
-        <v>0</v>
-      </c>
-      <c r="G47" s="34">
         <v>0</v>
       </c>
     </row>
@@ -4885,10 +4413,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5 F7 F9:F10 F12 F14 F16 F19 F21 F23 F25 F27 F29 F32:F1048576" xr:uid="{95F9219A-BB1D-427C-A5C7-0F9EDA01E71B}">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C30 C32:C1048576" xr:uid="{2E37FA97-16C9-4CD8-BF57-92BA0291CA83}">
       <formula1>"0,1"</formula1>
     </dataValidation>
@@ -4903,7 +4428,7 @@
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>A3:K3</xm:sqref>
+          <xm:sqref>G3:J3 A3:E3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
